--- a/excel-files/MAKATI/NEMESIO I. YABUT SENIOR HIGH SCHOOL.xlsx
+++ b/excel-files/MAKATI/NEMESIO I. YABUT SENIOR HIGH SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F922091-1D60-49DE-9DCB-CC86CE1522B0}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{577B8D01-87BD-49A6-90DF-66F5456010BF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="91">
   <si>
     <t>Grade Level</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>Personal Development</t>
+  </si>
+  <si>
+    <t>CO</t>
   </si>
   <si>
     <t>HOPE 1 and 2</t>
@@ -5178,21 +5181,25 @@
       <c r="B91" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C91" s="1"/>
+      <c r="C91" s="1">
+        <v>321</v>
+      </c>
       <c r="D91" s="1">
         <v>588</v>
       </c>
       <c r="E91" s="1">
         <v>2024</v>
       </c>
-      <c r="F91" s="5"/>
+      <c r="F91" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G91" s="3">
         <f t="shared" ref="G91:G98" si="18">IF((C91-D91)&lt;0,0,C91-D91)</f>
         <v>0</v>
       </c>
       <c r="H91" s="4">
         <f t="shared" ref="H91:H98" si="19">IF((D91-C91)&lt;0,0,D91-C91)</f>
-        <v>588</v>
+        <v>267</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="27.75" customHeight="1">
@@ -5200,7 +5207,7 @@
         <v>23</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -5220,23 +5227,27 @@
         <v>23</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C93" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C93" s="1">
+        <v>359</v>
+      </c>
       <c r="D93" s="1">
         <v>588</v>
       </c>
       <c r="E93" s="1">
         <v>2024</v>
       </c>
-      <c r="F93" s="5"/>
+      <c r="F93" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G93" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H93" s="4">
         <f t="shared" si="19"/>
-        <v>588</v>
+        <v>229</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="27.75" customHeight="1">
@@ -5244,23 +5255,27 @@
         <v>23</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C94" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C94" s="1">
+        <v>359</v>
+      </c>
       <c r="D94" s="1">
         <v>588</v>
       </c>
       <c r="E94" s="1">
         <v>2025</v>
       </c>
-      <c r="F94" s="5"/>
+      <c r="F94" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G94" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H94" s="4">
         <f t="shared" si="19"/>
-        <v>588</v>
+        <v>229</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="40.5" customHeight="1">
@@ -5268,23 +5283,27 @@
         <v>23</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C95" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="C95" s="1">
+        <v>359</v>
+      </c>
       <c r="D95" s="1">
         <v>588</v>
       </c>
       <c r="E95" s="1">
         <v>2025</v>
       </c>
-      <c r="F95" s="5"/>
+      <c r="F95" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G95" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H95" s="4">
         <f t="shared" si="19"/>
-        <v>588</v>
+        <v>229</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="38.25" customHeight="1">
@@ -5292,23 +5311,27 @@
         <v>23</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C96" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="C96" s="1">
+        <v>321</v>
+      </c>
       <c r="D96" s="1">
         <v>588</v>
       </c>
       <c r="E96" s="1">
         <v>2025</v>
       </c>
-      <c r="F96" s="5"/>
+      <c r="F96" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G96" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H96" s="4">
         <f t="shared" si="19"/>
-        <v>588</v>
+        <v>267</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="27.75" customHeight="1">
@@ -5316,23 +5339,27 @@
         <v>23</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C97" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C97" s="1">
+        <v>359</v>
+      </c>
       <c r="D97" s="1">
         <v>588</v>
       </c>
       <c r="E97" s="1">
         <v>2025</v>
       </c>
-      <c r="F97" s="5"/>
+      <c r="F97" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G97" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H97" s="4">
         <f t="shared" si="19"/>
-        <v>588</v>
+        <v>229</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="47.25" customHeight="1">
@@ -5340,23 +5367,27 @@
         <v>23</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C98" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="C98" s="1">
+        <v>321</v>
+      </c>
       <c r="D98" s="1">
         <v>588</v>
       </c>
       <c r="E98" s="1">
         <v>2024</v>
       </c>
-      <c r="F98" s="5"/>
+      <c r="F98" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G98" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H98" s="4">
         <f t="shared" si="19"/>
-        <v>588</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -5366,8 +5397,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5382,7 +5413,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5413,7 +5444,7 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="D1" s="42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1" s="42"/>
       <c r="F1" s="42"/>
@@ -5421,7 +5452,7 @@
       <c r="H1" s="42"/>
       <c r="I1" s="42"/>
       <c r="J1" s="43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -5429,7 +5460,7 @@
       <c r="N1" s="43"/>
       <c r="O1" s="43"/>
       <c r="P1" s="44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="44"/>
       <c r="R1" s="44"/>
@@ -5437,7 +5468,7 @@
       <c r="T1" s="44"/>
       <c r="U1" s="44"/>
       <c r="V1" s="45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W1" s="45"/>
       <c r="X1" s="45"/>
@@ -5456,81 +5487,81 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N2" s="40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y2" s="41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
@@ -6095,7 +6126,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="5">
@@ -6660,7 +6691,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="5">
@@ -7295,7 +7326,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -11892,7 +11923,7 @@
         <v>23</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="5">
@@ -11961,7 +11992,7 @@
         <v>23</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="5">
@@ -12030,7 +12061,7 @@
         <v>23</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="5">
@@ -12099,7 +12130,7 @@
         <v>23</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="5">
@@ -12168,7 +12199,7 @@
         <v>23</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="5">
@@ -12237,7 +12268,7 @@
         <v>23</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="5">
@@ -12306,7 +12337,7 @@
         <v>23</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="5">
@@ -13368,186 +13399,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13567,8 +13418,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13586,7 +13437,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13617,7 +13468,7 @@
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
       <c r="D1" s="42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1" s="42"/>
       <c r="F1" s="42"/>
@@ -13625,7 +13476,7 @@
       <c r="H1" s="42"/>
       <c r="I1" s="42"/>
       <c r="J1" s="43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -13633,7 +13484,7 @@
       <c r="N1" s="43"/>
       <c r="O1" s="43"/>
       <c r="P1" s="44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="44"/>
       <c r="R1" s="44"/>
@@ -13641,7 +13492,7 @@
       <c r="T1" s="44"/>
       <c r="U1" s="44"/>
       <c r="V1" s="45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W1" s="45"/>
       <c r="X1" s="45"/>
@@ -13660,76 +13511,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N2" s="40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y2" s="41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="19.149999999999999">
@@ -14220,7 +14071,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -14773,7 +14624,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -15395,7 +15246,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -15879,7 +15730,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -15948,7 +15799,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -16086,7 +15937,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16155,7 +16006,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16639,7 +16490,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -16708,7 +16559,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16846,7 +16697,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -16915,7 +16766,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -17399,7 +17250,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17468,7 +17319,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17606,7 +17457,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17675,7 +17526,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -18159,7 +18010,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18228,7 +18079,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18366,7 +18217,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18435,7 +18286,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -18919,7 +18770,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -18988,7 +18839,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19126,7 +18977,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19195,7 +19046,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19679,7 +19530,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -19748,7 +19599,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -19886,7 +19737,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -19955,7 +19806,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20439,7 +20290,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20508,7 +20359,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -20646,7 +20497,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -20715,7 +20566,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -20854,7 +20705,7 @@
         <v>23</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="5">
@@ -20923,7 +20774,7 @@
         <v>23</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -20992,7 +20843,7 @@
         <v>23</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -21061,7 +20912,7 @@
         <v>23</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -21130,7 +20981,7 @@
         <v>23</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -21199,7 +21050,7 @@
         <v>23</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -21268,7 +21119,7 @@
         <v>23</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -21843,186 +21694,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22040,8 +21711,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
